--- a/Assets/Excel/mining.xlsx
+++ b/Assets/Excel/mining.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>工作ID</t>
   </si>
@@ -96,6 +96,9 @@
     <t>地区名称</t>
   </si>
   <si>
+    <t>子地点名</t>
+  </si>
+  <si>
     <t>卡片标题</t>
   </si>
   <si>
@@ -129,6 +132,9 @@
     <t>sceneName</t>
   </si>
   <si>
+    <t>spotName</t>
+  </si>
+  <si>
     <t>displayName</t>
   </si>
   <si>
@@ -162,6 +168,9 @@
     <t>铜矿脉</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>铜矿脉 · 开采</t>
   </si>
   <si>
@@ -169,9 +178,6 @@
   </si>
   <si>
     <t>#B89468</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>mine_tin</t>
@@ -430,194 +436,212 @@
       <c r="L1" t="s">
         <v>35</v>
       </c>
+      <c r="M1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="M2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3">
         <v>4.5</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>6</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I3" t="s">
-        <v>51</v>
-      </c>
       <c r="J3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" t="s">
         <v>52</v>
       </c>
-      <c r="K3" t="s">
-        <v>53</v>
-      </c>
-      <c r="L3">
+      <c r="M3">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4">
         <v>5.5</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>9</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="I4" t="s">
-        <v>58</v>
-      </c>
       <c r="J4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
-      </c>
-      <c r="L4">
+        <v>61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5">
         <v>7</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>14</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>6</v>
       </c>
-      <c r="I5" t="s">
-        <v>64</v>
-      </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5">
+        <v>67</v>
+      </c>
+      <c r="L5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6">
         <v>10</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>22</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
-        <v>70</v>
-      </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6">
+        <v>73</v>
+      </c>
+      <c r="L6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
     </row>
@@ -633,50 +657,50 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -690,13 +714,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -710,13 +734,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -730,13 +754,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6">
         <v>1</v>

--- a/Assets/Excel/mining.xlsx
+++ b/Assets/Excel/mining.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>工作ID</t>
   </si>
@@ -111,7 +111,7 @@
     <t>解锁所需工作等级</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>详情文案(右侧)</t>
   </si>
   <si>
     <t>缩略图颜色</t>
@@ -123,6 +123,15 @@
     <t>消耗数量</t>
   </si>
   <si>
+    <t>金币概率0~1</t>
+  </si>
+  <si>
+    <t>金币最少</t>
+  </si>
+  <si>
+    <t>金币最多</t>
+  </si>
+  <si>
     <t>workId</t>
   </si>
   <si>
@@ -157,6 +166,15 @@
   </si>
   <si>
     <t>costAmount</t>
+  </si>
+  <si>
+    <t>goldChance</t>
+  </si>
+  <si>
+    <t>goldMin</t>
+  </si>
+  <si>
+    <t>goldMax</t>
   </si>
   <si>
     <t>mine_copper</t>
@@ -439,66 +457,84 @@
       <c r="M1" t="s">
         <v>36</v>
       </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>4.5</v>
@@ -510,36 +546,45 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" t="s">
         <v>58</v>
       </c>
-      <c r="E4" t="s">
-        <v>52</v>
-      </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>5.5</v>
@@ -551,36 +596,45 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -592,36 +646,45 @@
         <v>6</v>
       </c>
       <c r="J5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -633,15 +696,24 @@
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
         <v>0</v>
       </c>
     </row>
@@ -657,50 +729,50 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -714,13 +786,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -734,13 +806,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -754,13 +826,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D6">
         <v>1</v>

--- a/Assets/Excel/mining.xlsx
+++ b/Assets/Excel/mining.xlsx
@@ -10,7 +10,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>工作ID</t>
   </si>
@@ -114,7 +114,7 @@
     <t>详情文案(右侧)</t>
   </si>
   <si>
-    <t>缩略图颜色</t>
+    <t>缩略图(空=动作ID)</t>
   </si>
   <si>
     <t>消耗道具ID</t>
@@ -159,7 +159,7 @@
     <t>description</t>
   </si>
   <si>
-    <t>thumbColor</t>
+    <t>thumbImage</t>
   </si>
   <si>
     <t>costItemId</t>
@@ -195,9 +195,6 @@
     <t>洞口红土里的铜矿脉，矿镐敲下去就能剥出铜矿石，最适合新手练手。</t>
   </si>
   <si>
-    <t>#B89468</t>
-  </si>
-  <si>
     <t>mine_tin</t>
   </si>
   <si>
@@ -213,9 +210,6 @@
     <t>侧巷里的锡矿脉，色泽灰白，敲落即是锡矿石，常与铜矿混炼。</t>
   </si>
   <si>
-    <t>#A8A098</t>
-  </si>
-  <si>
     <t>mine_iron</t>
   </si>
   <si>
@@ -231,9 +225,6 @@
     <t>更深处的铁矿层，岩壁发黑，每镐下去必得铁矿石，锻打常用。</t>
   </si>
   <si>
-    <t>#585048</t>
-  </si>
-  <si>
     <t>mine_meteor</t>
   </si>
   <si>
@@ -247,9 +238,6 @@
   </si>
   <si>
     <t>矿洞尽头的陨铁矿壁，微光脉动，开采慢但每镐必出陨铁矿石。</t>
-  </si>
-  <si>
-    <t>#7060A0</t>
   </si>
   <si>
     <t>道具ID</t>
@@ -549,7 +537,7 @@
         <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L3" t="s">
         <v>58</v>
@@ -569,22 +557,22 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" t="s">
         <v>63</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" t="s">
         <v>64</v>
-      </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
       </c>
       <c r="G4">
         <v>5.5</v>
@@ -596,10 +584,10 @@
         <v>3</v>
       </c>
       <c r="J4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L4" t="s">
         <v>58</v>
@@ -619,22 +607,22 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
         <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" t="s">
-        <v>71</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -646,10 +634,10 @@
         <v>6</v>
       </c>
       <c r="J5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="L5" t="s">
         <v>58</v>
@@ -669,22 +657,22 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -696,10 +684,10 @@
         <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="L6" t="s">
         <v>58</v>
@@ -729,39 +717,39 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" t="s">
         <v>80</v>
-      </c>
-      <c r="C1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F2" t="s">
         <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -769,10 +757,10 @@
         <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -786,13 +774,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -806,13 +794,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -826,13 +814,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D6">
         <v>1</v>

--- a/Assets/Excel/mining.xlsx
+++ b/Assets/Excel/mining.xlsx
@@ -6,6 +6,8 @@
     <sheet name="works" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="actions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="loot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="work_levels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="action_levels" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -741,7 +743,6 @@
           <t>铜矿脉</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>铜矿脉 · 开采</t>
@@ -761,8 +762,6 @@
           <t>洞口红土里的铜矿脉，矿镐敲下去就能剥出铜矿石，最适合新手练手。</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0</v>
       </c>
@@ -797,7 +796,6 @@
           <t>锡矿脉</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>锡矿脉 · 开采</t>
@@ -817,8 +815,6 @@
           <t>侧巷里的锡矿脉，色泽灰白，敲落即是锡矿石，常与铜矿混炼。</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
@@ -853,7 +849,6 @@
           <t>铁矿层</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>铁矿层 · 开采</t>
@@ -873,8 +868,6 @@
           <t>更深处的铁矿层，岩壁发黑，每镐下去必得铁矿石，锻打常用。</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>0</v>
       </c>
@@ -909,7 +902,6 @@
           <t>陨铁矿</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>陨铁矿 · 开采</t>
@@ -929,8 +921,6 @@
           <t>矿洞尽头的陨铁矿壁，微光脉动，开采慢但每镐必出陨铁矿石。</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1129,4 +1119,2640 @@
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>升到下级所需经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5562</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5705</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5850</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5997</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6146</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6296</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6448</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6602</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6758</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>6916</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7076</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7237</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7565</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8070</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8242</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8416</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8592</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8770</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8949</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9130</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9313</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9498</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9684</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9872</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10062</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10254</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10448</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>10841</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>11241</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11444</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>11854</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>12062</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>12272</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>12484</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12698</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>12913</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>13130</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>13349</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>13570</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>13792</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>14016</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>14242</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>14470</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>14932</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>15165</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>15400</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>15637</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>15876</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>16116</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>16358</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>16602</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>16848</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>17096</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>17346</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>17597</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>17850</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>18105</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>18362</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>18620</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>18880</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>19142</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>19406</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>19672</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>19940</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>20209</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>20480</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>20753</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>21028</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>21304</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>21582</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>21862</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>22144</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>22428</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>22714</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>23001</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>23290</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>23581</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>23874</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>24168</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>24464</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>24762</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>25062</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>25364</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>25668</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>25973</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B162"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>升到下级所需经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>xp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2968</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>3401</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>4609</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5006</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5142</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5562</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5705</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5850</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5997</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6146</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6296</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6448</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6602</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6758</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>6916</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>7076</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>7237</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7565</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7732</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8070</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8242</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8416</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8592</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8770</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8949</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>9130</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9313</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>9498</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9684</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>9872</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10062</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10254</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10448</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>10841</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>11040</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>11241</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>11444</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>11648</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>11854</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>12062</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>12272</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>12484</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>12698</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>12913</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>13130</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>13349</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>13570</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>13792</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>14016</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>14242</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>14470</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>14932</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>15165</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>15400</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>15637</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>15876</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>16116</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>16358</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>16602</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>16848</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>17096</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>17346</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>17597</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>17850</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>18105</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>18362</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>18620</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>18880</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>19142</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>19406</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>19672</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>19940</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>20209</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>20480</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>20753</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>21028</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>21304</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>21582</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>21862</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>22144</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>22428</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>22714</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>23001</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>23290</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>23581</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>23874</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>24168</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>24464</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>24762</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>25062</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>25364</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>25668</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>25973</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+</worksheet>
 </file>
--- a/Assets/Excel/mining.xlsx
+++ b/Assets/Excel/mining.xlsx
@@ -443,22 +443,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>地区熟练度基数</t>
+          <t>动作熟练度基数</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>地区熟练度每级增量</t>
+          <t>动作熟练度每级增量</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否加工作XP(1/0)</t>
+          <t>是否加总等级XP(1/0)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>是否加地区XP(1/0)</t>
+          <t>是否加动作熟练度XP(1/0)</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>sceneXpBase</t>
+          <t>actionXpBase</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>sceneXpPerLevel</t>
+          <t>actionXpPerLevel</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>grantSceneXp</t>
+          <t>grantActionXp</t>
         </is>
       </c>
     </row>
